--- a/tests/testdata/excel/ファイル名/한글파일.xlsx
+++ b/tests/testdata/excel/ファイル名/한글파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76643E16-1F67-426F-9D38-EE9CB8DA15BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D012A22-5889-4FDE-B945-8CE7F06ABA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{C932F6E0-D357-46A6-9A57-93A9DE2C135F}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{91C56686-9165-45C7-B004-53260B511FE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{496F902F-FEDD-4C55-B65A-3FF9B513A6BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815400F-F6D2-45F4-ACB0-8698A4B41BBB}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/한글파일.xlsx
+++ b/tests/testdata/excel/ファイル名/한글파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D012A22-5889-4FDE-B945-8CE7F06ABA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0360BA46-6D05-4F10-AAC3-39141BE9AC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{91C56686-9165-45C7-B004-53260B511FE5}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{2FC35774-2819-4151-AADA-820FA512FD0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815400F-F6D2-45F4-ACB0-8698A4B41BBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC77AE95-0B44-4778-A45D-6CD2CB45265B}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
